--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="412">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1258,6 +1258,10 @@
   </si>
   <si>
     <t>If the administration is not instantaneous (rate is present), this can be specified to convey the total amount administered over period of time of a single administration.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>.doseQuantity</t>
@@ -7638,7 +7642,7 @@
         <v>366</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>100</v>
+        <v>396</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7647,18 +7651,18 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7681,16 +7685,16 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7740,7 +7744,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7761,18 +7765,18 @@
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7795,16 +7799,16 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7854,7 +7858,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7875,7 +7879,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-nimodipine-medication-administration-profile.xlsx
+++ b/StructureDefinition-nimodipine-medication-administration-profile.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
